--- a/lessons/sorting/excels/remarks_leo_star.xlsx
+++ b/lessons/sorting/excels/remarks_leo_star.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -- (10:57:30.402), -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~0.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -- (10:57:30.402) ~1.00, -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+        <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -187,7 +187,7 @@
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
+        <t>-var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -207,7 +207,7 @@
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
@@ -217,7 +217,7 @@
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
@@ -267,17 +267,17 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-0px (10:48:03.827), +0 (00:00:00)</t>
+        <t>-0px (10:48:03.827) ~0.33, +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+        <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
@@ -317,7 +317,7 @@
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H30" authorId="0" shapeId="0">
@@ -342,12 +342,12 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+        <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
-        <t>-1 (10:59:28.458), +0 (00:00:00)</t>
+        <t>-1 (10:59:28.458) ~0.00, +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -367,7 +367,7 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+        <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
@@ -377,7 +377,7 @@
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+        <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -397,7 +397,7 @@
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-column (10:22:03.223), +coloumn (00:00:00)</t>
+        <t>-column (10:22:03.223) ~0.86, +coloumn (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
@@ -457,7 +457,7 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
@@ -467,7 +467,7 @@
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -487,7 +487,7 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-html (10:12:23.484), +htm (00:00:00)</t>
+        <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
@@ -497,7 +497,7 @@
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H51" authorId="0" shapeId="0">
@@ -527,7 +527,7 @@
     </comment>
     <comment ref="Q56" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -547,17 +547,17 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:20:09.451), -: (10:47:38.437), -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
+        <t>-; (10:20:09.451), -: (10:47:38.437) ~1.00, -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="H62" authorId="0" shapeId="0">
@@ -582,7 +582,7 @@
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +700px (00:00:00)</t>
+        <t>-7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +700px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q66" authorId="0" shapeId="0">
@@ -607,12 +607,12 @@
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-0px (10:48:03.827), +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
+        <t>-0px (10:48:03.827) ~0.33, +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -updateBars (11:12:30.664), -100 (11:14:24.924), +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993), -updateBars (11:12:30.664) ~0.90, -100 (11:14:24.924) ~0.67, +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -632,17 +632,17 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+        <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-200px (10:20:09.051), -background (10:44:24.231), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +500px (00:00:00), +Background (00:00:00)</t>
+        <t>-200px (10:20:09.051) ~0.80, -background (10:44:24.231) ~0.90, +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +500px (00:00:00), +Background (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="J71" authorId="0" shapeId="0">
@@ -672,17 +672,17 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-123456 (10:19:55.544), -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +654321 (00:00:00)</t>
+        <t>-123456 (10:19:55.544) ~0.00, -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -document (10:37:47.323), -123456 (10:38:22.251), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -123456 (10:38:22.251) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="J73" authorId="0" shapeId="0">
@@ -712,7 +712,7 @@
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-createElement (10:39:45.021), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+        <t>-createElement (10:39:45.021) ~0.93, -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -752,7 +752,7 @@
     </comment>
     <comment ref="Q79" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H81" authorId="0" shapeId="0">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -- (10:57:30.402), -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~0.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -- (10:57:30.402) ~1.00, -end (10:57:30.432), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +- (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
+          <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
+          <t>-var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-0px (10:48:03.827), +0 (00:00:00)</t>
+          <t>-0px (10:48:03.827) ~0.33, +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+          <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+          <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-1 (10:59:28.458), +0 (00:00:00)</t>
+          <t>-1 (10:59:28.458) ~0.00, +0 (00:00:00)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+          <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+          <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-column (10:22:03.223), +coloumn (00:00:00)</t>
+          <t>-column (10:22:03.223) ~0.86, +coloumn (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-html (10:12:23.484), +htm (00:00:00)</t>
+          <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-; (10:20:09.451), -: (10:47:38.437), -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
+          <t>-; (10:20:09.451), -: (10:47:38.437) ~1.00, -- (10:57:30.402), +- (00:00:00), +: (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +700px (00:00:00)</t>
+          <t>-7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +700px (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-0px (10:48:03.827), +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
+          <t>-0px (10:48:03.827) ~0.33, +: (00:00:00), +; (00:00:00), +background (00:00:00), +red (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920), -getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -updateBars (11:12:30.664), -100 (11:14:24.924), +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993), -updateBars (11:12:30.664) ~0.90, -100 (11:14:24.924) ~0.67, +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+          <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-200px (10:20:09.051), -background (10:44:24.231), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +500px (00:00:00), +Background (00:00:00)</t>
+          <t>-200px (10:20:09.051) ~0.80, -background (10:44:24.231) ~0.90, +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +500px (00:00:00), +Background (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-123456 (10:19:55.544), -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +654321 (00:00:00)</t>
+          <t>-123456 (10:19:55.544) ~0.00, -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -document (10:37:47.323), -123456 (10:38:22.251), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -123456 (10:38:22.251) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-createElement (10:39:45.021), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857), +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+          <t>-createElement (10:39:45.021) ~0.93, -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">

--- a/lessons/sorting/excels/remarks_leo_star.xlsx
+++ b/lessons/sorting/excels/remarks_leo_star.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,14 @@
     </font>
     <font>
       <name val="Segoe UI Emoji"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,11 +66,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1241,24 +1252,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1279,24 +1272,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1349,11 +1324,9 @@
           <t>+- (00:00:00), +arry (00:00:00), +center (00:00:00), +content (00:00:00), +cretaeElement (00:00:00), +justify (00:00:00), -flex (10:21:58.800), -i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -- (10:57:30.402), -end (10:57:30.432), -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>100</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>72.3</v>
       </c>
@@ -1370,12 +1343,11 @@
           <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -let (10:59:27.295), -} (10:59:37.396), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +arry (00:00:00), +cretaeElement (00:00:00)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1423,15 +1395,12 @@
           <t>+let (00:00:00), -var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>100</v>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>100</v>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>95.90000000000001</v>
       </c>
@@ -1440,12 +1409,11 @@
           <t>-var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1462,22 +1430,6 @@
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1493,24 +1445,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1531,24 +1465,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1630,12 +1546,11 @@
           <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,24 +1566,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1689,24 +1586,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1735,7 +1614,6 @@
       <c r="E12" t="n">
         <v>2.1</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -1755,7 +1633,6 @@
           <t>-&lt; (10:12:09.435), -! (10:12:12.136), -DOCTYPE (10:12:14.338), -html (10:12:15.511), -&gt; (10:12:15.872)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>93.09999999999999</v>
       </c>
@@ -1767,17 +1644,14 @@
       <c r="O12" t="n">
         <v>100</v>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1793,24 +1667,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1832,22 +1688,6 @@
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1863,24 +1703,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1901,24 +1723,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1939,24 +1743,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1977,24 +1763,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2034,7 +1802,6 @@
       <c r="H19" t="n">
         <v>100</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -2043,15 +1810,12 @@
           <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:14:32.118)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>100</v>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>100</v>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
         <v>97.90000000000001</v>
       </c>
@@ -2060,12 +1824,11 @@
           <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:14:32.118)</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2081,24 +1844,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2180,12 +1925,11 @@
           <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2201,24 +1945,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2239,24 +1965,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2285,7 +1993,6 @@
       <c r="E24" t="n">
         <v>24.7</v>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>99.5</v>
       </c>
@@ -2305,15 +2012,12 @@
           <t>-; (10:42:36.565)</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>100</v>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
         <v>100</v>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
         <v>99.7</v>
       </c>
@@ -2322,12 +2026,11 @@
           <t>-; (10:42:36.565)</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2375,11 +2078,9 @@
           <t>+ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00), -length (10:38:57.372), -classList (10:42:32.670), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>100</v>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>84.59999999999999</v>
       </c>
@@ -2396,12 +2097,11 @@
           <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2417,24 +2117,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2455,24 +2137,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2494,22 +2158,6 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2525,24 +2173,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2571,7 +2201,6 @@
       <c r="E30" t="n">
         <v>0.2</v>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>99.8</v>
       </c>
@@ -2586,26 +2215,20 @@
       <c r="J30" t="n">
         <v>100</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>100</v>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>100</v>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
         <v>100</v>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
+      <c r="S30" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2669,7 +2292,6 @@
       <c r="O31" t="n">
         <v>100</v>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>99.7</v>
       </c>
@@ -2678,12 +2300,11 @@
           <t>-1 (10:59:28.458) ~0.00, +0 (00:00:00)</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2699,24 +2320,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2737,24 +2340,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2775,24 +2360,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2813,24 +2380,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2883,7 +2432,6 @@
           <t>+, (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +20 (00:00:00), +aee (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), +sorting (00:00:00), -Sorting (10:13:13.802), -50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982)</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>97.2</v>
       </c>
@@ -2908,12 +2456,11 @@
           <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S36" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2929,24 +2476,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2967,24 +2496,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3005,24 +2516,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3043,24 +2536,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3082,22 +2557,6 @@
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3132,7 +2591,6 @@
       <c r="H42" t="n">
         <v>100</v>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>87.40000000000001</v>
       </c>
@@ -3141,7 +2599,6 @@
           <t>+/ (00:00:00), +coloumn (00:00:00), -column (10:22:03.223), -let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100)</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -3166,12 +2623,11 @@
           <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100)</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S42" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3187,24 +2643,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3225,24 +2663,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3271,7 +2691,6 @@
       <c r="E45" t="n">
         <v>0.5</v>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>99.5</v>
       </c>
@@ -3291,15 +2710,12 @@
           <t>-; (11:10:17.104)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>100</v>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>100</v>
       </c>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
         <v>99.7</v>
       </c>
@@ -3308,12 +2724,11 @@
           <t>-; (11:10:17.104)</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+      <c r="S45" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3361,11 +2776,9 @@
           <t>-flex (10:21:58.800), -display (10:47:38.305), -: (10:47:38.437), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>100</v>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
         <v>81.5</v>
       </c>
@@ -3377,13 +2790,11 @@
       <c r="Q46" t="n">
         <v>100</v>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr">
+      <c r="S46" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3400,22 +2811,6 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3450,7 +2845,6 @@
       <c r="H48" t="n">
         <v>100</v>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
         <v>91.40000000000001</v>
       </c>
@@ -3459,7 +2853,6 @@
           <t>+arry (00:00:00), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +getElementByClassName (00:00:00), +tittle (00:00:00), +visualizer (00:00:00), -title (10:12:49.434), -Visualizer (10:13:16.993), -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -array (10:28:45.898), -document (10:37:47.323), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891)</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>97.2</v>
       </c>
@@ -3484,12 +2877,11 @@
           <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>C1&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3505,24 +2897,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3575,7 +2949,6 @@
           <t>+10 (00:00:00), +getElementsByClassname (00:00:00), +htm (00:00:00), -html (10:12:23.484), -- (10:57:30.402), -end (10:57:30.432), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -3600,12 +2973,11 @@
           <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S50" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3629,7 +3001,6 @@
       <c r="E51" t="n">
         <v>0.5</v>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>99.8</v>
       </c>
@@ -3644,26 +3015,20 @@
       <c r="J51" t="n">
         <v>100</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>100</v>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>100</v>
       </c>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
         <v>100</v>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr">
+      <c r="S51" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3679,24 +3044,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3717,24 +3064,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3755,24 +3084,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3793,24 +3104,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3863,7 +3156,6 @@
           <t>+10 (00:00:00), -&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -; (10:50:48.660), -100 (11:14:24.924)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>90.3</v>
       </c>
@@ -3875,7 +3167,6 @@
       <c r="O56" t="n">
         <v>100</v>
       </c>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
         <v>99.3</v>
       </c>
@@ -3884,12 +3175,11 @@
           <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S56" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3905,24 +3195,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3943,24 +3215,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4013,11 +3267,9 @@
           <t>+- (00:00:00), +: (00:00:00), +; (00:00:00), +getElementsByClassname (00:00:00), +lenght (00:00:00), -; (10:20:09.451), -length (10:38:57.372), -: (10:47:38.437), -- (10:57:30.402), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118)</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>100</v>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>92.3</v>
       </c>
@@ -4034,12 +3286,11 @@
           <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S59" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4055,24 +3306,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4094,22 +3327,6 @@
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4133,7 +3350,6 @@
       <c r="E62" t="n">
         <v>0.7</v>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>99.8</v>
       </c>
@@ -4148,7 +3364,6 @@
       <c r="J62" t="n">
         <v>100</v>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>A</t>
@@ -4157,21 +3372,17 @@
       <c r="M62" t="n">
         <v>100</v>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>100</v>
       </c>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
         <v>100</v>
       </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr">
+      <c r="S62" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4187,24 +3398,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4225,24 +3418,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4263,24 +3438,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4333,11 +3490,9 @@
           <t>+700px (00:00:00), -7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198)</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>100</v>
       </c>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
         <v>83.09999999999999</v>
       </c>
@@ -4354,12 +3509,11 @@
           <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198)</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S66" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4375,24 +3529,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4453,7 +3589,6 @@
       <c r="M68" t="n">
         <v>100</v>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>92.3</v>
       </c>
@@ -4470,12 +3605,11 @@
           <t>-bubbleSort (10:57:42.836) ~0.90, -- (10:59:44.058), -bubbleSort (11:08:34.118), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -document (11:09:24.920) ~0.10, -getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993), -updateBars (11:12:30.664) ~0.90, -100 (11:14:24.924) ~0.67, +updataBars (00:00:00), +visualizer (00:00:00), +querySelectorAll (00:00:00), +. (00:00:00), +bubblesort (00:00:00), +0 (00:00:00), ++ (00:00:00), ++ (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr"/>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4491,24 +3625,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4561,7 +3677,6 @@
           <t>+500px (00:00:00), +&gt; (00:00:00), +Background (00:00:00), +Doctype (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00), +sorting (00:00:00), +visualizer (00:00:00), +visualizer (00:00:00), -DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -200px (10:20:09.051), -&lt; (10:27:15.917), -background (10:44:24.231), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982)</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>93.09999999999999</v>
       </c>
@@ -4586,12 +3701,11 @@
           <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S70" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4615,14 +3729,12 @@
       <c r="E71" t="n">
         <v>0</v>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>99.5</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>99.8</v>
       </c>
@@ -4631,15 +3743,12 @@
           <t>-; (11:10:17.104)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>100</v>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
         <v>100</v>
       </c>
-      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
         <v>99.7</v>
       </c>
@@ -4648,12 +3757,11 @@
           <t>-; (11:10:17.104)</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S71" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4688,7 +3796,6 @@
       <c r="H72" t="n">
         <v>100</v>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
         <v>90.7</v>
       </c>
@@ -4697,7 +3804,6 @@
           <t>+654321 (00:00:00), +654321 (00:00:00), +654321 (00:00:00), +arry (00:00:00), +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +getElementByClassName (00:00:00), +tittle (00:00:00), +visualizer (00:00:00), -title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), -123456 (10:19:55.544), -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -array (10:28:45.898), -document (10:37:47.323), -123456 (10:38:22.251), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178), -getElementsByClassName (11:09:28.891)</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>95.8</v>
       </c>
@@ -4722,12 +3828,11 @@
           <t>-array (10:28:45.898) ~0.80, -document (10:37:47.323) ~0.75, -123456 (10:38:22.251) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +)* (11:08:31.588), +;* (11:08:31.589), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +documnet (00:00:00), +654321 (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr"/>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>C1&lt;</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4751,14 +3856,12 @@
       <c r="E73" t="n">
         <v>0</v>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
         <v>99.5</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>99.8</v>
       </c>
@@ -4767,7 +3870,6 @@
           <t>-! (10:12:12.136)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -4779,17 +3881,14 @@
       <c r="O73" t="n">
         <v>100</v>
       </c>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="n">
         <v>100</v>
       </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr">
+      <c r="S73" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4805,24 +3904,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4862,7 +3943,6 @@
       <c r="H75" t="n">
         <v>100</v>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
         <v>86.2</v>
       </c>
@@ -4871,11 +3951,9 @@
           <t>+ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +createrElement (00:00:00), +get (00:00:00), +setTimeOut (00:00:00), +updatebars (00:00:00), -flex (10:21:58.800), -align (10:24:12.446), -items (10:24:13.500), -createElement (10:39:45.021), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -; (10:47:39.811), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -- (10:57:30.282), -: (10:57:30.342), -- (10:57:30.402), -end (10:57:30.432), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -setTimeout (11:14:18.857)</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
         <v>100</v>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
         <v>72.3</v>
       </c>
@@ -4892,12 +3970,11 @@
           <t>-createElement (10:39:45.021) ~0.93, -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -} (11:08:40.006), -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +updatebars (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S75" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4913,24 +3990,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4951,24 +4010,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5008,7 +4049,6 @@
       <c r="H78" t="n">
         <v>100</v>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
         <v>99.5</v>
       </c>
@@ -5017,7 +4057,6 @@
           <t>+/ (00:00:00), += (00:00:00)</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -5029,7 +4068,6 @@
       <c r="O78" t="n">
         <v>100</v>
       </c>
-      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
         <v>99.7</v>
       </c>
@@ -5038,12 +4076,11 @@
           <t>+= (00:00:00)</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S78" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5091,15 +4128,12 @@
           <t>+10 (00:00:00), -; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924)</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>100</v>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>100</v>
       </c>
-      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="n">
         <v>99</v>
       </c>
@@ -5108,12 +4142,11 @@
           <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S79" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5129,24 +4162,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5175,7 +4190,6 @@
       <c r="E81" t="n">
         <v>0.5</v>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>99.09999999999999</v>
       </c>
@@ -5203,11 +4217,9 @@
       <c r="M81" t="n">
         <v>100</v>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>100</v>
       </c>
-      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="n">
         <v>99</v>
       </c>
@@ -5216,12 +4228,11 @@
           <t>-; (11:02:17.463), -; (11:10:17.104), -; (11:14:32.118)</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S81" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5245,7 +4256,6 @@
       <c r="E82" t="n">
         <v>3.3</v>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>99.8</v>
       </c>
@@ -5260,7 +4270,6 @@
       <c r="J82" t="n">
         <v>100</v>
       </c>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>Q</t>
@@ -5269,21 +4278,17 @@
       <c r="M82" t="n">
         <v>100</v>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
         <v>100</v>
       </c>
-      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
         <v>100</v>
       </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr">
+      <c r="S82" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5331,15 +4336,12 @@
           <t>-; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104)</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>100</v>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
         <v>100</v>
       </c>
-      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
         <v>95.90000000000001</v>
       </c>
@@ -5348,12 +4350,11 @@
           <t>-; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104)</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S83" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5369,24 +4370,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5407,24 +4390,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5446,22 +4411,6 @@
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
       <c r="V86" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5483,22 +4432,6 @@
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5520,22 +4453,6 @@
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
       <c r="V88" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5557,22 +4474,6 @@
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5594,22 +4495,6 @@
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5631,22 +4516,6 @@
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5668,22 +4537,6 @@
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5705,22 +4558,6 @@
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5742,22 +4579,6 @@
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5779,22 +4600,6 @@
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5816,22 +4621,6 @@
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5853,22 +4642,6 @@
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5890,22 +4663,6 @@
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5927,22 +4684,6 @@
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5964,22 +4705,6 @@
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
           <t>LLM</t>
